--- a/test/fixtures/in-wpi-mini.xlsx
+++ b/test/fixtures/in-wpi-mini.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,310 +413,615 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Wholesale Price Index (2022-23=100)</t>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Commodity Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Commodity Code</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Commodity Weight</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Aug-26</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>COMM_NAME</t>
-        </is>
+      <c r="A2" t="n">
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>COMM_CODE</t>
+          <t>Iron Ore</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>COMM_WT</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>INDX072026</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>INDX082026</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>INDX092026</t>
-        </is>
+          <t>1103010005</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>131.3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>All commodities</t>
-        </is>
+      <c r="A3" t="n">
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1000000000</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+          <t>Zinc concentrate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1103010003</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>147.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Coking Coal</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1201010100</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>90.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>b. Non-Coking Coal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1201020000</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>89.90000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Petroleum Coke</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1202010010</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>87.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hot Rolled Steel Coils/Sheets/Strips</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1314010010</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>87.90000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hot Rolled Plates (≤600 mm width)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1314010011</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>101.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cold Rolled Steel Coils/Sheets/Strips</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1314010012</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>98.40000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GP/GC sheet</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1314010013</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>87.90000000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bars and Rods of Mild steel</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1314010014</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>82.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MS Wire Rods</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1314010015</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>90</v>
+      </c>
+      <c r="F12" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Angles, Channels, Sections</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1314010016</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>95</v>
+      </c>
+      <c r="F13" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Steel Pipes &amp; Tubes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1314010020</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>99</v>
+      </c>
+      <c r="F14" t="n">
+        <v>98.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Scrap Iron/Steel</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1314010027</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>78.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stainless Steel Coils, Strips &amp; Sheets</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1314010031</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>86.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Copper cathodes and sections of cathodes</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1314020002</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>152.6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>159.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Aluminium ingot</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1314020005</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>120</v>
+      </c>
+      <c r="F18" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Aluminium foils</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1314020010</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>130.6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>127.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Zinc ingot</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1314020007</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>110</v>
+      </c>
+      <c r="F20" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lead ingot</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1314020008</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E21" t="n">
         <v>100</v>
       </c>
-      <c r="D3" t="n">
-        <v>104.1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>104.5</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="F21" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Copper bars, rods &amp; wire rods</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1315080004</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>140.7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>140.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PVC pipe</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1312030002</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>89.90000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Lead Pencil</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1322070004</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E24" t="n">
         <v>104.9</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Iron ore</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1102010000</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="F4" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Coking coal</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2101010000</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>110</v>
-      </c>
-      <c r="E5" t="n">
-        <v>111</v>
-      </c>
-      <c r="F5" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>HR coils &amp; sheets, including narrow strip</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3707020101</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>100.8</v>
-      </c>
-      <c r="F6" t="n">
-        <v>100.2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CR coils &amp; sheets, including narrow strip</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3707020102</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>103</v>
-      </c>
-      <c r="E7" t="n">
-        <v>102.5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>102.9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GP/GC sheets</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3707020103</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>99</v>
-      </c>
-      <c r="E8" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>98.7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MS wire rods</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3707020201</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>105</v>
-      </c>
-      <c r="E9" t="n">
-        <v>104</v>
-      </c>
-      <c r="F9" t="n">
-        <v>104.4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Bars &amp; rods</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3707020202</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D10" t="n">
-        <v>106</v>
-      </c>
-      <c r="E10" t="n">
-        <v>105.5</v>
-      </c>
-      <c r="F10" t="n">
-        <v>105.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Pipes &amp; tubes</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3707030101</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>102</v>
-      </c>
-      <c r="E11" t="n">
-        <v>102</v>
-      </c>
-      <c r="F11" t="n">
-        <v>101.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Stainless steel - coils, strips &amp; sheets</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3707040101</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>97</v>
-      </c>
-      <c r="E12" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>96.09999999999999</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Aluminium ingot</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3708010101</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>110</v>
-      </c>
-      <c r="E13" t="n">
-        <v>111.2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>112</v>
+      <c r="F24" t="n">
+        <v>105.9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Glass Bangles</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1313010010</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>118.8</v>
       </c>
     </row>
   </sheetData>

--- a/test/fixtures/in-wpi-mini.xlsx
+++ b/test/fixtures/in-wpi-mini.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,22 +742,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Steel Pipes &amp; Tubes</t>
+          <t>Scrap Iron/Steel</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1314010020</t>
+          <t>1314010027</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E14" t="n">
-        <v>99</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>98.5</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="15">
@@ -766,22 +766,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Scrap Iron/Steel</t>
+          <t>Stainless Steel Coils, Strips &amp; Sheets</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1314010027</t>
+          <t>1314010031</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>84.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>78.5</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="16">
@@ -790,22 +790,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stainless Steel Coils, Strips &amp; Sheets</t>
+          <t>Copper cathodes and sections of cathodes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1314010031</t>
+          <t>1314020002</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E16" t="n">
-        <v>94.90000000000001</v>
+        <v>152.6</v>
       </c>
       <c r="F16" t="n">
-        <v>86.7</v>
+        <v>159.6</v>
       </c>
     </row>
     <row r="17">
@@ -814,22 +814,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Copper cathodes and sections of cathodes</t>
+          <t>Aluminium ingot</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1314020002</t>
+          <t>1314020005</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.3</v>
       </c>
       <c r="E17" t="n">
-        <v>152.6</v>
+        <v>120</v>
       </c>
       <c r="F17" t="n">
-        <v>159.6</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18">
@@ -838,22 +838,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aluminium ingot</t>
+          <t>Aluminium foils</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1314020005</t>
+          <t>1314020010</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>120</v>
+        <v>130.6</v>
       </c>
       <c r="F18" t="n">
-        <v>121</v>
+        <v>127.1</v>
       </c>
     </row>
     <row r="19">
@@ -862,22 +862,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aluminium foils</t>
+          <t>Copper bars, rods &amp; wire rods</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1314020010</t>
+          <t>1315080004</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>130.6</v>
+        <v>140.7</v>
       </c>
       <c r="F19" t="n">
-        <v>127.1</v>
+        <v>140.2</v>
       </c>
     </row>
     <row r="20">
@@ -886,22 +886,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zinc ingot</t>
+          <t>PVC pipe</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1314020007</t>
+          <t>1312030002</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>110</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>111</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -910,22 +910,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lead ingot</t>
+          <t>Lead Pencil</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1314020008</t>
+          <t>1322070004</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="F21" t="n">
-        <v>101</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="22">
@@ -934,22 +934,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Copper bars, rods &amp; wire rods</t>
+          <t>Glass Bangles</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1315080004</t>
+          <t>1313010010</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>140.7</v>
+        <v>118.8</v>
       </c>
       <c r="F22" t="n">
-        <v>140.2</v>
+        <v>118.8</v>
       </c>
     </row>
     <row r="23">
@@ -958,22 +958,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PVC pipe</t>
+          <t>Pipes, tubes &amp; casing of steel/iron</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1312030002</t>
+          <t>1314030008</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E23" t="n">
-        <v>88.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="F23" t="n">
-        <v>89.90000000000001</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -982,22 +982,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lead Pencil</t>
+          <t>Brass tubes and pipes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1322070004</t>
+          <t>1314030010</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.1</v>
       </c>
       <c r="E24" t="n">
-        <v>104.9</v>
+        <v>159.8</v>
       </c>
       <c r="F24" t="n">
-        <v>105.9</v>
+        <v>165.2</v>
       </c>
     </row>
     <row r="25">
@@ -1006,22 +1006,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Glass Bangles</t>
+          <t>Non-Alloyed Zinc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1313010010</t>
+          <t>1314020007</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0.1</v>
       </c>
       <c r="E25" t="n">
-        <v>118.8</v>
+        <v>130</v>
       </c>
       <c r="F25" t="n">
-        <v>118.8</v>
+        <v>140.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Refined Lead</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1314020006</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>108</v>
+      </c>
+      <c r="F26" t="n">
+        <v>109.5</v>
       </c>
     </row>
   </sheetData>
